--- a/rh/reportes/archivos/PLANTILLA NOMBRAMIENTO ADMINISTRATIVO.xlsx
+++ b/rh/reportes/archivos/PLANTILLA NOMBRAMIENTO ADMINISTRATIVO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerardo\Documents\INAES\repositorio\SIA_V2\rh\reportes\archivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078F137C-A5DF-4804-AF1A-445106357321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9F7EC2-110A-4860-9625-4A053118467C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2955" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOMBRAMIENTO" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
   <si>
     <t>CONSTANCIA DE NOMBRAMIENTO</t>
   </si>
@@ -414,109 +414,108 @@
     <t>C.</t>
   </si>
   <si>
-    <t>%FOLIO%</t>
-  </si>
-  <si>
-    <t>%FECHA%</t>
-  </si>
-  <si>
-    <t>%APPATERNO%</t>
-  </si>
-  <si>
-    <t>%APMATERNO%</t>
-  </si>
-  <si>
-    <t>%NOMBRE%</t>
-  </si>
-  <si>
-    <t>%RFC%</t>
-  </si>
-  <si>
-    <t>%CURP%</t>
-  </si>
-  <si>
-    <t>%ESTADOCIVIL%</t>
-  </si>
-  <si>
-    <t>%NACIONALIDAD%</t>
-  </si>
-  <si>
-    <t>%SEXO%</t>
-  </si>
-  <si>
-    <t>%EDAD%</t>
-  </si>
-  <si>
-    <t>%CALLE%</t>
-  </si>
-  <si>
-    <t>%COLONIA%</t>
-  </si>
-  <si>
-    <t>%CP%</t>
-  </si>
-  <si>
-    <t>%MUNICIPIO%</t>
-  </si>
-  <si>
-    <t>%ENTIDAD%</t>
-  </si>
-  <si>
-    <t>%TELEFONO%</t>
-  </si>
-  <si>
-    <t>%PLAZA%</t>
-  </si>
-  <si>
-    <t>%NOMBRAMIENTO%</t>
-  </si>
-  <si>
-    <t>%ADSCRIPCION%</t>
-  </si>
-  <si>
-    <t>%NUMPLAZA%</t>
-  </si>
-  <si>
-    <t>%CC%</t>
-  </si>
-  <si>
-    <t>%CLAVEPRESUPUESTAL%</t>
-  </si>
-  <si>
-    <t>%CODPLAZA%</t>
-  </si>
-  <si>
-    <t>%DENPUESTO%</t>
-  </si>
-  <si>
-    <t>%NIVEL%</t>
-  </si>
-  <si>
-    <t>%RADICACION%</t>
-  </si>
-  <si>
-    <t>%SUELDOBASE%</t>
-  </si>
-  <si>
-    <t>%ESTIMULO%</t>
-  </si>
-  <si>
-    <t>%COMPGARANTIZADA%</t>
-  </si>
-  <si>
-    <t>%TOTALBRUTO%</t>
-  </si>
-  <si>
-    <t>%FECHAINICIO%</t>
+    <t>APPATERNO_D</t>
+  </si>
+  <si>
+    <t>APMATERNO_D</t>
+  </si>
+  <si>
+    <t>FOLIO_D</t>
+  </si>
+  <si>
+    <t>FECHA_D</t>
+  </si>
+  <si>
+    <t>NOMBRE_D</t>
+  </si>
+  <si>
+    <t>RFC_D</t>
+  </si>
+  <si>
+    <t>CURP_D</t>
+  </si>
+  <si>
+    <t>ESTADOCIVIL_D</t>
+  </si>
+  <si>
+    <t>NACIONALIDAD_D</t>
+  </si>
+  <si>
+    <t>SEXO_D</t>
+  </si>
+  <si>
+    <t>EDAD_D</t>
+  </si>
+  <si>
+    <t>CALLE_D</t>
+  </si>
+  <si>
+    <t>COLONIA_D</t>
+  </si>
+  <si>
+    <t>CP_D</t>
+  </si>
+  <si>
+    <t>MUNICIPIO_D</t>
+  </si>
+  <si>
+    <t>ENTIDAD_D</t>
+  </si>
+  <si>
+    <t>TELEFONO_D</t>
+  </si>
+  <si>
+    <t>PLAZA_D</t>
+  </si>
+  <si>
+    <t>NOMBRAMIENTO_D</t>
+  </si>
+  <si>
+    <t>ADSCRIPCION_D</t>
+  </si>
+  <si>
+    <t>NUMPLAZA_D</t>
+  </si>
+  <si>
+    <t>CC_D</t>
+  </si>
+  <si>
+    <t>CLAVEPRESUPUESTAL_D</t>
+  </si>
+  <si>
+    <t>CODPLAZA_D</t>
+  </si>
+  <si>
+    <t>DENPUESTO_D</t>
+  </si>
+  <si>
+    <t>NIVEL_D</t>
+  </si>
+  <si>
+    <t>RADICACION_D</t>
+  </si>
+  <si>
+    <t>FECHAINICIO_D</t>
+  </si>
+  <si>
+    <t>SUELDOBASE_D</t>
+  </si>
+  <si>
+    <t>ESTIMULO_D</t>
+  </si>
+  <si>
+    <t>COMPGARANTIZADA_D</t>
+  </si>
+  <si>
+    <t>TOTALBRUTO_D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -878,7 +877,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -933,143 +932,137 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2350,27 +2343,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
       <c r="U1" s="1"/>
     </row>
     <row r="2" spans="2:55" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2421,20 +2414,20 @@
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
@@ -2449,20 +2442,20 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
@@ -2496,26 +2489,26 @@
       <c r="AH5" s="11"/>
     </row>
     <row r="6" spans="2:55" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
       <c r="AG6" s="10"/>
     </row>
     <row r="7" spans="2:55" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2542,31 +2535,31 @@
       <c r="AG7" s="10"/>
     </row>
     <row r="8" spans="2:55" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46" t="s">
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46" t="s">
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="O8" s="46"/>
-      <c r="P8" s="46"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46"/>
-      <c r="T8" s="46"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
       <c r="X8" s="11"/>
       <c r="Y8" s="10"/>
       <c r="Z8" s="10"/>
@@ -2591,31 +2584,31 @@
       <c r="AU8" s="11"/>
     </row>
     <row r="9" spans="2:55" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47" t="s">
+      <c r="B9" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="47"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
       <c r="X9" s="11"/>
       <c r="Y9" s="10"/>
       <c r="Z9" s="10"/>
@@ -2640,37 +2633,37 @@
       <c r="AU9" s="11"/>
     </row>
     <row r="10" spans="2:55" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45" t="s">
+      <c r="C10" s="43"/>
+      <c r="D10" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45" t="s">
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45" t="s">
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45" t="s">
+      <c r="M10" s="43"/>
+      <c r="N10" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45" t="s">
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="T10" s="45"/>
+      <c r="T10" s="43"/>
       <c r="X10" s="11"/>
       <c r="Y10" s="10"/>
       <c r="Z10" s="10"/>
@@ -2695,37 +2688,37 @@
       <c r="AU10" s="11"/>
     </row>
     <row r="11" spans="2:55" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="48" t="s">
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="47" t="s">
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47" t="s">
+      <c r="M11" s="45"/>
+      <c r="N11" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47" t="s">
+      <c r="O11" s="45"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="45"/>
+      <c r="R11" s="45"/>
+      <c r="S11" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="T11" s="47"/>
+      <c r="T11" s="45"/>
       <c r="X11" s="11"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
@@ -2750,27 +2743,27 @@
       <c r="AU11" s="11"/>
     </row>
     <row r="12" spans="2:55" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
       <c r="U12" s="17"/>
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
@@ -2788,31 +2781,31 @@
       <c r="AU12" s="11"/>
     </row>
     <row r="13" spans="2:55" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45" t="s">
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45" t="s">
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="T13" s="45"/>
+      <c r="T13" s="43"/>
       <c r="AH13" s="11"/>
       <c r="AK13" s="11"/>
       <c r="AL13" s="11"/>
@@ -2827,31 +2820,31 @@
       <c r="AU13" s="11"/>
     </row>
     <row r="14" spans="2:55" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="47" t="s">
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="53" t="s">
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="T14" s="53"/>
+      <c r="T14" s="45"/>
       <c r="AH14" s="11"/>
       <c r="AK14" s="11"/>
       <c r="AL14" s="11"/>
@@ -2866,31 +2859,31 @@
       <c r="AU14" s="11"/>
     </row>
     <row r="15" spans="2:55" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45" t="s">
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45" t="s">
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="T15" s="45"/>
+      <c r="T15" s="43"/>
       <c r="AH15" s="11"/>
       <c r="AK15" s="11"/>
       <c r="AL15" s="11"/>
@@ -2905,31 +2898,31 @@
       <c r="AU15" s="11"/>
     </row>
     <row r="16" spans="2:55" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47" t="s">
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47" t="s">
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="45"/>
+      <c r="R16" s="45"/>
+      <c r="S16" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="T16" s="47"/>
+      <c r="T16" s="45"/>
       <c r="AH16" s="11"/>
       <c r="AK16" s="11"/>
       <c r="AL16" s="11"/>
@@ -2944,27 +2937,27 @@
       <c r="AU16" s="11"/>
     </row>
     <row r="17" spans="2:47" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="49"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
       <c r="U17" s="17"/>
       <c r="V17" s="18"/>
       <c r="W17" s="11"/>
@@ -2982,33 +2975,33 @@
       <c r="AU17" s="11"/>
     </row>
     <row r="18" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45" t="s">
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45" t="s">
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45" t="s">
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="T18" s="45"/>
+      <c r="T18" s="43"/>
       <c r="AG18" s="10"/>
       <c r="AH18" s="11"/>
       <c r="AK18" s="11"/>
@@ -3024,33 +3017,33 @@
       <c r="AU18" s="11"/>
     </row>
     <row r="19" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="47" t="s">
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47" t="s">
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="55" t="s">
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="45"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="45"/>
+      <c r="R19" s="45"/>
+      <c r="S19" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="T19" s="55"/>
+      <c r="T19" s="51"/>
       <c r="AG19" s="10"/>
       <c r="AH19" s="11"/>
       <c r="AK19" s="11"/>
@@ -3069,32 +3062,32 @@
       <c r="B20" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="56" t="s">
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="57"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="56" t="s">
+      <c r="J20" s="53"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="57"/>
-      <c r="S20" s="59" t="s">
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="T20" s="59"/>
+      <c r="T20" s="55"/>
       <c r="AG20" s="10"/>
       <c r="AH20" s="11"/>
       <c r="AK20" s="11"/>
@@ -3110,35 +3103,35 @@
       <c r="AU20" s="11"/>
     </row>
     <row r="21" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="50" t="s">
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="J21" s="51"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="50" t="s">
+      <c r="J21" s="49"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="M21" s="51"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="60" t="s">
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="T21" s="61"/>
+      <c r="T21" s="57"/>
       <c r="AG21" s="10"/>
       <c r="AH21" s="11"/>
       <c r="AK21" s="11"/>
@@ -3154,30 +3147,30 @@
       <c r="AU21" s="11"/>
     </row>
     <row r="22" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45" t="s">
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="62"/>
-      <c r="T22" s="62"/>
-      <c r="W22" s="21"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="58"/>
+      <c r="T22" s="58"/>
+      <c r="W22" s="20"/>
       <c r="AG22" s="10"/>
       <c r="AH22" s="11"/>
       <c r="AK22" s="11"/>
@@ -3193,30 +3186,30 @@
       <c r="AU22" s="11"/>
     </row>
     <row r="23" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="47" t="s">
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
-      <c r="W23" s="22"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="45"/>
+      <c r="W23" s="21"/>
       <c r="AG23" s="10"/>
       <c r="AH23" s="11"/>
       <c r="AK23" s="11"/>
@@ -3232,30 +3225,30 @@
       <c r="AU23" s="11"/>
     </row>
     <row r="24" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45" t="s">
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45" t="s">
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
       <c r="T24" s="19" t="s">
         <v>31</v>
       </c>
@@ -3275,26 +3268,26 @@
       <c r="AU24" s="11"/>
     </row>
     <row r="25" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47"/>
-      <c r="S25" s="47"/>
-      <c r="T25" s="23" t="s">
-        <v>86</v>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="61"/>
+      <c r="R25" s="61"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="38" t="s">
+        <v>82</v>
       </c>
       <c r="AG25" s="10"/>
       <c r="AH25" s="11"/>
@@ -3311,27 +3304,27 @@
       <c r="AU25" s="11"/>
     </row>
     <row r="26" spans="2:47" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="47"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47"/>
+      <c r="S26" s="47"/>
+      <c r="T26" s="47"/>
       <c r="U26" s="17"/>
       <c r="W26" s="17"/>
       <c r="X26" s="17"/>
@@ -3350,36 +3343,36 @@
       <c r="AU26" s="11"/>
     </row>
     <row r="27" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45" t="s">
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="45" t="s">
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45" t="s">
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="43"/>
+      <c r="W27" s="22"/>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="22"/>
       <c r="AG27" s="10"/>
       <c r="AH27" s="11"/>
       <c r="AK27" s="11"/>
@@ -3395,36 +3388,36 @@
       <c r="AU27" s="11"/>
     </row>
     <row r="28" spans="2:47" s="13" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="65"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65" t="s">
+      <c r="B28" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65" t="s">
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="M28" s="65"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="65"/>
-      <c r="P28" s="65"/>
-      <c r="Q28" s="65" t="s">
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="R28" s="63"/>
-      <c r="S28" s="63"/>
-      <c r="T28" s="63"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="R28" s="59"/>
+      <c r="S28" s="59"/>
+      <c r="T28" s="59"/>
       <c r="W28" s="10"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
+      <c r="X28" s="22"/>
+      <c r="Y28" s="22"/>
       <c r="AG28" s="10"/>
       <c r="AH28" s="11"/>
       <c r="AK28" s="11"/>
@@ -3440,30 +3433,30 @@
       <c r="AU28" s="11"/>
     </row>
     <row r="29" spans="2:47" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="66"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="66"/>
-      <c r="N29" s="66"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="66"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="62"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="62"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="62"/>
+      <c r="R29" s="62"/>
+      <c r="S29" s="62"/>
+      <c r="T29" s="62"/>
       <c r="U29" s="17"/>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
+      <c r="X29" s="22"/>
+      <c r="Y29" s="22"/>
       <c r="Z29" s="13"/>
       <c r="AC29" s="13"/>
       <c r="AH29" s="11"/>
@@ -3480,31 +3473,31 @@
       <c r="AU29" s="11"/>
     </row>
     <row r="30" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="64" t="s">
+      <c r="B30" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="64"/>
-      <c r="R30" s="64"/>
-      <c r="S30" s="64"/>
-      <c r="T30" s="64"/>
-      <c r="U30" s="25"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
+      <c r="L30" s="60"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="60"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="60"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="60"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="23"/>
       <c r="W30" s="10"/>
-      <c r="X30" s="24"/>
-      <c r="Y30" s="24"/>
+      <c r="X30" s="22"/>
+      <c r="Y30" s="22"/>
       <c r="AG30" s="10"/>
       <c r="AH30" s="11"/>
       <c r="AK30" s="11"/>
@@ -3520,30 +3513,30 @@
       <c r="AU30" s="11"/>
     </row>
     <row r="31" spans="2:47" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="68"/>
-      <c r="M31" s="68"/>
-      <c r="N31" s="68"/>
-      <c r="O31" s="68"/>
-      <c r="P31" s="68"/>
-      <c r="Q31" s="68"/>
-      <c r="R31" s="68"/>
-      <c r="S31" s="68"/>
-      <c r="T31" s="68"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="64"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="64"/>
+      <c r="Q31" s="64"/>
+      <c r="R31" s="64"/>
+      <c r="S31" s="64"/>
+      <c r="T31" s="64"/>
       <c r="U31" s="17"/>
-      <c r="X31" s="24"/>
-      <c r="Y31" s="24"/>
+      <c r="X31" s="22"/>
+      <c r="Y31" s="22"/>
       <c r="AC31" s="13"/>
       <c r="AH31" s="11"/>
       <c r="AK31" s="11"/>
@@ -3559,32 +3552,34 @@
       <c r="AU31" s="11"/>
     </row>
     <row r="32" spans="2:47" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="45" t="s">
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="65"/>
+      <c r="L32" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="63"/>
-      <c r="P32" s="63"/>
-      <c r="Q32" s="63"/>
-      <c r="R32" s="63"/>
-      <c r="S32" s="63"/>
-      <c r="T32" s="63"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="66"/>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="66"/>
       <c r="W32" s="10"/>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="22"/>
       <c r="AG32" s="10"/>
       <c r="AH32" s="11"/>
       <c r="AK32" s="11"/>
@@ -3600,31 +3595,31 @@
       <c r="AU32" s="11"/>
     </row>
     <row r="33" spans="2:47" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="69"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="69"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
-      <c r="R33" s="69"/>
-      <c r="S33" s="69"/>
-      <c r="T33" s="69"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
+      <c r="I33" s="67"/>
+      <c r="J33" s="67"/>
+      <c r="K33" s="67"/>
+      <c r="L33" s="67"/>
+      <c r="M33" s="67"/>
+      <c r="N33" s="67"/>
+      <c r="O33" s="67"/>
+      <c r="P33" s="67"/>
+      <c r="Q33" s="67"/>
+      <c r="R33" s="67"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="67"/>
       <c r="U33" s="17"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="27"/>
-      <c r="Y33" s="27"/>
+      <c r="W33" s="24"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
       <c r="AC33" s="13"/>
       <c r="AH33" s="11"/>
       <c r="AK33" s="11"/>
@@ -3640,30 +3635,30 @@
       <c r="AU33" s="11"/>
     </row>
     <row r="34" spans="2:47" s="13" customFormat="1" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="47"/>
-      <c r="W34" s="28"/>
-      <c r="X34" s="29"/>
-      <c r="Y34" s="29"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="61"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="61"/>
+      <c r="S34" s="61"/>
+      <c r="T34" s="61"/>
+      <c r="W34" s="26"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="27"/>
       <c r="AG34" s="10"/>
       <c r="AH34" s="11"/>
       <c r="AK34" s="11"/>
@@ -3679,29 +3674,29 @@
       <c r="AU34" s="11"/>
     </row>
     <row r="35" spans="2:47" s="13" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="71"/>
-      <c r="S35" s="71"/>
-      <c r="T35" s="71"/>
-      <c r="U35" s="25"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="69"/>
+      <c r="M35" s="69"/>
+      <c r="N35" s="69"/>
+      <c r="O35" s="69"/>
+      <c r="P35" s="69"/>
+      <c r="Q35" s="69"/>
+      <c r="R35" s="69"/>
+      <c r="S35" s="69"/>
+      <c r="T35" s="69"/>
+      <c r="U35" s="23"/>
       <c r="W35" s="10"/>
-      <c r="X35" s="24"/>
-      <c r="Y35" s="24"/>
+      <c r="X35" s="22"/>
+      <c r="Y35" s="22"/>
       <c r="AH35" s="11"/>
       <c r="AK35" s="11"/>
       <c r="AL35" s="11"/>
@@ -3716,29 +3711,29 @@
       <c r="AU35" s="11"/>
     </row>
     <row r="36" spans="2:47" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="72"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="72"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="72"/>
-      <c r="P36" s="72"/>
-      <c r="Q36" s="72"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="72"/>
-      <c r="T36" s="72"/>
-      <c r="U36" s="31"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="29"/>
-      <c r="Y36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
+      <c r="S36" s="70"/>
+      <c r="T36" s="70"/>
+      <c r="U36" s="29"/>
+      <c r="W36" s="26"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="27"/>
       <c r="AH36" s="11"/>
       <c r="AK36" s="11"/>
       <c r="AL36" s="11"/>
@@ -3753,30 +3748,30 @@
       <c r="AU36" s="11"/>
     </row>
     <row r="37" spans="2:47" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
       <c r="V37" s="10"/>
       <c r="W37" s="10"/>
-      <c r="X37" s="24"/>
-      <c r="Y37" s="24"/>
+      <c r="X37" s="22"/>
+      <c r="Y37" s="22"/>
       <c r="AH37" s="11"/>
       <c r="AK37" s="11"/>
       <c r="AL37" s="11"/>
@@ -3791,28 +3786,28 @@
       <c r="AU37" s="11"/>
     </row>
     <row r="38" spans="2:47" s="13" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-      <c r="N38" s="31"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="31"/>
-      <c r="Q38" s="31"/>
-      <c r="R38" s="31"/>
-      <c r="S38" s="31"/>
-      <c r="T38" s="31"/>
-      <c r="U38" s="31"/>
-      <c r="AA38" s="24"/>
-      <c r="AB38" s="24"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
+      <c r="AA38" s="22"/>
+      <c r="AB38" s="22"/>
       <c r="AH38" s="11"/>
       <c r="AK38" s="11"/>
       <c r="AL38" s="11"/>
@@ -3827,28 +3822,28 @@
       <c r="AU38" s="11"/>
     </row>
     <row r="39" spans="2:47" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="73"/>
-      <c r="K39" s="73"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="74"/>
-      <c r="N39" s="74"/>
-      <c r="O39" s="74"/>
-      <c r="P39" s="74"/>
-      <c r="Q39" s="74"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="AA39" s="24"/>
-      <c r="AB39" s="24"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="72"/>
+      <c r="N39" s="72"/>
+      <c r="O39" s="72"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="29"/>
+      <c r="AA39" s="22"/>
+      <c r="AB39" s="22"/>
       <c r="AH39" s="11"/>
       <c r="AK39" s="11"/>
       <c r="AL39" s="11"/>
@@ -3863,37 +3858,37 @@
       <c r="AU39" s="11"/>
     </row>
     <row r="40" spans="2:47" s="13" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="67" t="s">
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="67" t="s">
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="N40" s="67"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
-      <c r="R40" s="67" t="s">
+      <c r="N40" s="63"/>
+      <c r="O40" s="63"/>
+      <c r="P40" s="63"/>
+      <c r="Q40" s="63"/>
+      <c r="R40" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="S40" s="67"/>
-      <c r="T40" s="67"/>
-      <c r="U40" s="31"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="63"/>
+      <c r="U40" s="29"/>
       <c r="W40" s="17"/>
-      <c r="X40" s="24"/>
-      <c r="Y40" s="34"/>
-      <c r="Z40" s="24"/>
-      <c r="AA40" s="24"/>
+      <c r="X40" s="22"/>
+      <c r="Y40" s="32"/>
+      <c r="Z40" s="22"/>
+      <c r="AA40" s="22"/>
       <c r="AH40" s="11"/>
       <c r="AK40" s="11"/>
       <c r="AL40" s="11"/>
@@ -3908,34 +3903,34 @@
       <c r="AU40" s="11"/>
     </row>
     <row r="41" spans="2:47" s="13" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="84" t="s">
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84" t="s">
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="82"/>
+      <c r="K41" s="82"/>
+      <c r="L41" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="M41" s="84"/>
-      <c r="N41" s="84"/>
-      <c r="O41" s="84"/>
-      <c r="P41" s="84"/>
-      <c r="Q41" s="84"/>
-      <c r="R41" s="84" t="s">
+      <c r="M41" s="82"/>
+      <c r="N41" s="82"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="82"/>
+      <c r="Q41" s="82"/>
+      <c r="R41" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="S41" s="84"/>
-      <c r="T41" s="84"/>
-      <c r="U41" s="31"/>
+      <c r="S41" s="82"/>
+      <c r="T41" s="82"/>
+      <c r="U41" s="29"/>
       <c r="W41" s="17"/>
-      <c r="X41" s="24"/>
+      <c r="X41" s="22"/>
       <c r="AH41" s="11"/>
       <c r="AK41" s="11"/>
       <c r="AL41" s="11"/>
@@ -3950,30 +3945,30 @@
       <c r="AU41" s="11"/>
     </row>
     <row r="42" spans="2:47" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84"/>
-      <c r="K42" s="84"/>
-      <c r="L42" s="84"/>
-      <c r="M42" s="84"/>
-      <c r="N42" s="84"/>
-      <c r="O42" s="84"/>
-      <c r="P42" s="84"/>
-      <c r="Q42" s="84"/>
-      <c r="R42" s="84"/>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="25"/>
-      <c r="Y42" s="24"/>
-      <c r="Z42" s="24"/>
-      <c r="AA42" s="24"/>
-      <c r="AB42" s="24"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
+      <c r="I42" s="82"/>
+      <c r="J42" s="82"/>
+      <c r="K42" s="82"/>
+      <c r="L42" s="82"/>
+      <c r="M42" s="82"/>
+      <c r="N42" s="82"/>
+      <c r="O42" s="82"/>
+      <c r="P42" s="82"/>
+      <c r="Q42" s="82"/>
+      <c r="R42" s="82"/>
+      <c r="S42" s="82"/>
+      <c r="T42" s="82"/>
+      <c r="U42" s="23"/>
+      <c r="Y42" s="22"/>
+      <c r="Z42" s="22"/>
+      <c r="AA42" s="22"/>
+      <c r="AB42" s="22"/>
       <c r="AH42" s="11"/>
       <c r="AK42" s="11"/>
       <c r="AL42" s="11"/>
@@ -3988,32 +3983,32 @@
       <c r="AU42" s="11"/>
     </row>
     <row r="43" spans="2:47" s="13" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="85"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="85"/>
-      <c r="E43" s="85"/>
-      <c r="F43" s="85"/>
-      <c r="G43" s="85"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="85"/>
-      <c r="J43" s="85"/>
-      <c r="K43" s="85"/>
-      <c r="L43" s="85"/>
-      <c r="M43" s="85"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="85"/>
-      <c r="P43" s="85"/>
-      <c r="Q43" s="85"/>
-      <c r="R43" s="85"/>
-      <c r="S43" s="85"/>
-      <c r="T43" s="85"/>
-      <c r="U43" s="85"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="83"/>
+      <c r="L43" s="83"/>
+      <c r="M43" s="83"/>
+      <c r="N43" s="83"/>
+      <c r="O43" s="83"/>
+      <c r="P43" s="83"/>
+      <c r="Q43" s="83"/>
+      <c r="R43" s="83"/>
+      <c r="S43" s="83"/>
+      <c r="T43" s="83"/>
+      <c r="U43" s="83"/>
       <c r="W43" s="17"/>
       <c r="X43" s="17"/>
       <c r="Y43" s="18"/>
-      <c r="Z43" s="24"/>
-      <c r="AA43" s="24"/>
-      <c r="AB43" s="24"/>
+      <c r="Z43" s="22"/>
+      <c r="AA43" s="22"/>
+      <c r="AB43" s="22"/>
       <c r="AH43" s="11"/>
       <c r="AK43" s="11"/>
       <c r="AL43" s="11"/>
@@ -4028,32 +4023,32 @@
       <c r="AU43" s="11"/>
     </row>
     <row r="44" spans="2:47" s="13" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
-      <c r="N44" s="25"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="25"/>
-      <c r="Q44" s="25"/>
-      <c r="R44" s="25"/>
-      <c r="S44" s="25"/>
-      <c r="T44" s="25"/>
-      <c r="U44" s="25"/>
-      <c r="W44" s="34"/>
-      <c r="X44" s="24"/>
-      <c r="Y44" s="24"/>
-      <c r="Z44" s="24"/>
-      <c r="AA44" s="24"/>
-      <c r="AB44" s="24"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="23"/>
+      <c r="O44" s="23"/>
+      <c r="P44" s="23"/>
+      <c r="Q44" s="23"/>
+      <c r="R44" s="23"/>
+      <c r="S44" s="23"/>
+      <c r="T44" s="23"/>
+      <c r="U44" s="23"/>
+      <c r="W44" s="32"/>
+      <c r="X44" s="22"/>
+      <c r="Y44" s="22"/>
+      <c r="Z44" s="22"/>
+      <c r="AA44" s="22"/>
+      <c r="AB44" s="22"/>
       <c r="AH44" s="11"/>
       <c r="AK44" s="11"/>
       <c r="AL44" s="11"/>
@@ -4068,32 +4063,32 @@
       <c r="AU44" s="11"/>
     </row>
     <row r="45" spans="2:47" s="13" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="85"/>
-      <c r="C45" s="85"/>
-      <c r="D45" s="85"/>
-      <c r="E45" s="85"/>
-      <c r="F45" s="85"/>
-      <c r="G45" s="85"/>
-      <c r="H45" s="85"/>
-      <c r="I45" s="85"/>
-      <c r="J45" s="85"/>
-      <c r="K45" s="85"/>
-      <c r="L45" s="85"/>
-      <c r="M45" s="85"/>
-      <c r="N45" s="85"/>
-      <c r="O45" s="85"/>
-      <c r="P45" s="85"/>
-      <c r="Q45" s="85"/>
-      <c r="R45" s="85"/>
-      <c r="S45" s="85"/>
-      <c r="T45" s="85"/>
-      <c r="U45" s="85"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="83"/>
+      <c r="J45" s="83"/>
+      <c r="K45" s="83"/>
+      <c r="L45" s="83"/>
+      <c r="M45" s="83"/>
+      <c r="N45" s="83"/>
+      <c r="O45" s="83"/>
+      <c r="P45" s="83"/>
+      <c r="Q45" s="83"/>
+      <c r="R45" s="83"/>
+      <c r="S45" s="83"/>
+      <c r="T45" s="83"/>
+      <c r="U45" s="83"/>
       <c r="W45" s="17"/>
-      <c r="X45" s="24"/>
-      <c r="Y45" s="24"/>
-      <c r="Z45" s="24"/>
-      <c r="AA45" s="24"/>
-      <c r="AB45" s="24"/>
+      <c r="X45" s="22"/>
+      <c r="Y45" s="22"/>
+      <c r="Z45" s="22"/>
+      <c r="AA45" s="22"/>
+      <c r="AB45" s="22"/>
       <c r="AH45" s="11"/>
       <c r="AK45" s="11"/>
       <c r="AL45" s="11"/>
@@ -4108,33 +4103,33 @@
       <c r="AU45" s="11"/>
     </row>
     <row r="46" spans="2:47" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="86" t="s">
+      <c r="B46" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="87"/>
-      <c r="D46" s="87"/>
-      <c r="E46" s="87"/>
-      <c r="F46" s="87"/>
-      <c r="G46" s="87"/>
-      <c r="H46" s="87"/>
-      <c r="I46" s="87"/>
-      <c r="J46" s="87"/>
-      <c r="K46" s="87"/>
-      <c r="L46" s="87"/>
-      <c r="M46" s="87"/>
-      <c r="N46" s="87"/>
-      <c r="O46" s="87"/>
-      <c r="P46" s="87"/>
-      <c r="Q46" s="87"/>
-      <c r="R46" s="87"/>
-      <c r="S46" s="87"/>
-      <c r="T46" s="88"/>
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="85"/>
+      <c r="H46" s="85"/>
+      <c r="I46" s="85"/>
+      <c r="J46" s="85"/>
+      <c r="K46" s="85"/>
+      <c r="L46" s="85"/>
+      <c r="M46" s="85"/>
+      <c r="N46" s="85"/>
+      <c r="O46" s="85"/>
+      <c r="P46" s="85"/>
+      <c r="Q46" s="85"/>
+      <c r="R46" s="85"/>
+      <c r="S46" s="85"/>
+      <c r="T46" s="86"/>
       <c r="W46" s="17"/>
-      <c r="X46" s="24"/>
-      <c r="Y46" s="24"/>
-      <c r="Z46" s="24"/>
-      <c r="AA46" s="24"/>
-      <c r="AB46" s="24"/>
+      <c r="X46" s="22"/>
+      <c r="Y46" s="22"/>
+      <c r="Z46" s="22"/>
+      <c r="AA46" s="22"/>
+      <c r="AB46" s="22"/>
       <c r="AH46" s="11"/>
       <c r="AK46" s="11"/>
       <c r="AL46" s="11"/>
@@ -4149,429 +4144,429 @@
       <c r="AU46" s="11"/>
     </row>
     <row r="47" spans="2:47" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="35"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="36"/>
-      <c r="N47" s="36"/>
-      <c r="O47" s="36"/>
-      <c r="P47" s="36"/>
-      <c r="Q47" s="36"/>
-      <c r="R47" s="36"/>
-      <c r="S47" s="36"/>
-      <c r="T47" s="37"/>
-      <c r="W47" s="34"/>
-      <c r="X47" s="24"/>
-      <c r="Y47" s="24"/>
-      <c r="Z47" s="24"/>
-      <c r="AA47" s="24"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="34"/>
+      <c r="N47" s="34"/>
+      <c r="O47" s="34"/>
+      <c r="P47" s="34"/>
+      <c r="Q47" s="34"/>
+      <c r="R47" s="34"/>
+      <c r="S47" s="34"/>
+      <c r="T47" s="35"/>
+      <c r="W47" s="32"/>
+      <c r="X47" s="22"/>
+      <c r="Y47" s="22"/>
+      <c r="Z47" s="22"/>
+      <c r="AA47" s="22"/>
       <c r="AB47" s="13"/>
     </row>
     <row r="48" spans="2:47" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="35"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="36"/>
-      <c r="M48" s="36"/>
-      <c r="N48" s="36"/>
-      <c r="O48" s="36"/>
-      <c r="P48" s="36"/>
-      <c r="Q48" s="36"/>
-      <c r="R48" s="36"/>
-      <c r="S48" s="36"/>
-      <c r="T48" s="37"/>
-      <c r="W48" s="34"/>
-      <c r="X48" s="24"/>
-      <c r="Y48" s="24"/>
-      <c r="Z48" s="24"/>
-      <c r="AA48" s="24"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="34"/>
+      <c r="K48" s="34"/>
+      <c r="L48" s="34"/>
+      <c r="M48" s="34"/>
+      <c r="N48" s="34"/>
+      <c r="O48" s="34"/>
+      <c r="P48" s="34"/>
+      <c r="Q48" s="34"/>
+      <c r="R48" s="34"/>
+      <c r="S48" s="34"/>
+      <c r="T48" s="35"/>
+      <c r="W48" s="32"/>
+      <c r="X48" s="22"/>
+      <c r="Y48" s="22"/>
+      <c r="Z48" s="22"/>
+      <c r="AA48" s="22"/>
       <c r="AB48" s="13"/>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B49" s="75" t="s">
+      <c r="B49" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="C49" s="76"/>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="76"/>
-      <c r="I49" s="76"/>
-      <c r="J49" s="76"/>
-      <c r="K49" s="76"/>
-      <c r="L49" s="76"/>
-      <c r="M49" s="76"/>
-      <c r="N49" s="76"/>
-      <c r="O49" s="76"/>
-      <c r="P49" s="76"/>
-      <c r="Q49" s="76"/>
-      <c r="R49" s="76"/>
-      <c r="S49" s="76"/>
-      <c r="T49" s="77"/>
+      <c r="C49" s="74"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="74"/>
+      <c r="K49" s="74"/>
+      <c r="L49" s="74"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="74"/>
+      <c r="P49" s="74"/>
+      <c r="Q49" s="74"/>
+      <c r="R49" s="74"/>
+      <c r="S49" s="74"/>
+      <c r="T49" s="75"/>
       <c r="W49" s="13"/>
-      <c r="X49" s="24"/>
-      <c r="Y49" s="24"/>
-      <c r="Z49" s="24"/>
-      <c r="AA49" s="24"/>
+      <c r="X49" s="22"/>
+      <c r="Y49" s="22"/>
+      <c r="Z49" s="22"/>
+      <c r="AA49" s="22"/>
       <c r="AB49" s="13"/>
     </row>
     <row r="50" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B50" s="38"/>
-      <c r="T50" s="39"/>
-      <c r="W50" s="34"/>
-      <c r="X50" s="34"/>
+      <c r="B50" s="36"/>
+      <c r="T50" s="37"/>
+      <c r="W50" s="32"/>
+      <c r="X50" s="32"/>
       <c r="Y50" s="18"/>
       <c r="Z50" s="13"/>
       <c r="AA50" s="13"/>
       <c r="AB50" s="13"/>
     </row>
     <row r="51" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="78" t="s">
+      <c r="B51" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="79"/>
-      <c r="D51" s="79"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="79"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="79"/>
-      <c r="I51" s="79"/>
-      <c r="J51" s="79"/>
-      <c r="K51" s="79"/>
-      <c r="L51" s="79"/>
-      <c r="M51" s="79"/>
-      <c r="N51" s="79"/>
-      <c r="O51" s="79"/>
-      <c r="P51" s="79"/>
-      <c r="Q51" s="79"/>
-      <c r="R51" s="79"/>
-      <c r="S51" s="79"/>
-      <c r="T51" s="80"/>
-      <c r="W51" s="34"/>
-      <c r="X51" s="24"/>
-      <c r="Y51" s="24"/>
-      <c r="Z51" s="24"/>
-      <c r="AA51" s="24"/>
-      <c r="AB51" s="24"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="77"/>
+      <c r="E51" s="77"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="77"/>
+      <c r="I51" s="77"/>
+      <c r="J51" s="77"/>
+      <c r="K51" s="77"/>
+      <c r="L51" s="77"/>
+      <c r="M51" s="77"/>
+      <c r="N51" s="77"/>
+      <c r="O51" s="77"/>
+      <c r="P51" s="77"/>
+      <c r="Q51" s="77"/>
+      <c r="R51" s="77"/>
+      <c r="S51" s="77"/>
+      <c r="T51" s="78"/>
+      <c r="W51" s="32"/>
+      <c r="X51" s="22"/>
+      <c r="Y51" s="22"/>
+      <c r="Z51" s="22"/>
+      <c r="AA51" s="22"/>
+      <c r="AB51" s="22"/>
     </row>
     <row r="52" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B52" s="78"/>
-      <c r="C52" s="79"/>
-      <c r="D52" s="79"/>
-      <c r="E52" s="79"/>
-      <c r="F52" s="79"/>
-      <c r="G52" s="79"/>
-      <c r="H52" s="79"/>
-      <c r="I52" s="79"/>
-      <c r="J52" s="79"/>
-      <c r="K52" s="79"/>
-      <c r="L52" s="79"/>
-      <c r="M52" s="79"/>
-      <c r="N52" s="79"/>
-      <c r="O52" s="79"/>
-      <c r="P52" s="79"/>
-      <c r="Q52" s="79"/>
-      <c r="R52" s="79"/>
-      <c r="S52" s="79"/>
-      <c r="T52" s="80"/>
+      <c r="B52" s="76"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="77"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="77"/>
+      <c r="I52" s="77"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="77"/>
+      <c r="L52" s="77"/>
+      <c r="M52" s="77"/>
+      <c r="N52" s="77"/>
+      <c r="O52" s="77"/>
+      <c r="P52" s="77"/>
+      <c r="Q52" s="77"/>
+      <c r="R52" s="77"/>
+      <c r="S52" s="77"/>
+      <c r="T52" s="78"/>
       <c r="W52" s="17"/>
-      <c r="X52" s="24"/>
-      <c r="Y52" s="24"/>
-      <c r="Z52" s="24"/>
-      <c r="AA52" s="24"/>
-      <c r="AB52" s="24"/>
+      <c r="X52" s="22"/>
+      <c r="Y52" s="22"/>
+      <c r="Z52" s="22"/>
+      <c r="AA52" s="22"/>
+      <c r="AB52" s="22"/>
     </row>
     <row r="53" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B53" s="78"/>
-      <c r="C53" s="79"/>
-      <c r="D53" s="79"/>
-      <c r="E53" s="79"/>
-      <c r="F53" s="79"/>
-      <c r="G53" s="79"/>
-      <c r="H53" s="79"/>
-      <c r="I53" s="79"/>
-      <c r="J53" s="79"/>
-      <c r="K53" s="79"/>
-      <c r="L53" s="79"/>
-      <c r="M53" s="79"/>
-      <c r="N53" s="79"/>
-      <c r="O53" s="79"/>
-      <c r="P53" s="79"/>
-      <c r="Q53" s="79"/>
-      <c r="R53" s="79"/>
-      <c r="S53" s="79"/>
-      <c r="T53" s="80"/>
-      <c r="W53" s="21"/>
-      <c r="X53" s="24"/>
-      <c r="Y53" s="34"/>
-      <c r="Z53" s="24"/>
-      <c r="AA53" s="24"/>
-      <c r="AB53" s="24"/>
+      <c r="B53" s="76"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="77"/>
+      <c r="E53" s="77"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="77"/>
+      <c r="I53" s="77"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="77"/>
+      <c r="L53" s="77"/>
+      <c r="M53" s="77"/>
+      <c r="N53" s="77"/>
+      <c r="O53" s="77"/>
+      <c r="P53" s="77"/>
+      <c r="Q53" s="77"/>
+      <c r="R53" s="77"/>
+      <c r="S53" s="77"/>
+      <c r="T53" s="78"/>
+      <c r="W53" s="20"/>
+      <c r="X53" s="22"/>
+      <c r="Y53" s="32"/>
+      <c r="Z53" s="22"/>
+      <c r="AA53" s="22"/>
+      <c r="AB53" s="22"/>
     </row>
     <row r="54" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B54" s="78"/>
-      <c r="C54" s="79"/>
-      <c r="D54" s="79"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="79"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
-      <c r="I54" s="79"/>
-      <c r="J54" s="79"/>
-      <c r="K54" s="79"/>
-      <c r="L54" s="79"/>
-      <c r="M54" s="79"/>
-      <c r="N54" s="79"/>
-      <c r="O54" s="79"/>
-      <c r="P54" s="79"/>
-      <c r="Q54" s="79"/>
-      <c r="R54" s="79"/>
-      <c r="S54" s="79"/>
-      <c r="T54" s="80"/>
+      <c r="B54" s="76"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="77"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="77"/>
+      <c r="H54" s="77"/>
+      <c r="I54" s="77"/>
+      <c r="J54" s="77"/>
+      <c r="K54" s="77"/>
+      <c r="L54" s="77"/>
+      <c r="M54" s="77"/>
+      <c r="N54" s="77"/>
+      <c r="O54" s="77"/>
+      <c r="P54" s="77"/>
+      <c r="Q54" s="77"/>
+      <c r="R54" s="77"/>
+      <c r="S54" s="77"/>
+      <c r="T54" s="78"/>
       <c r="W54" s="13"/>
       <c r="X54" s="13"/>
       <c r="Y54" s="13"/>
-      <c r="Z54" s="24"/>
-      <c r="AA54" s="24"/>
-      <c r="AB54" s="24"/>
+      <c r="Z54" s="22"/>
+      <c r="AA54" s="22"/>
+      <c r="AB54" s="22"/>
     </row>
     <row r="55" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B55" s="78"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="79"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="79"/>
-      <c r="G55" s="79"/>
-      <c r="H55" s="79"/>
-      <c r="I55" s="79"/>
-      <c r="J55" s="79"/>
-      <c r="K55" s="79"/>
-      <c r="L55" s="79"/>
-      <c r="M55" s="79"/>
-      <c r="N55" s="79"/>
-      <c r="O55" s="79"/>
-      <c r="P55" s="79"/>
-      <c r="Q55" s="79"/>
-      <c r="R55" s="79"/>
-      <c r="S55" s="79"/>
-      <c r="T55" s="80"/>
-      <c r="W55" s="34"/>
-      <c r="X55" s="24"/>
-      <c r="Y55" s="24"/>
-      <c r="Z55" s="24"/>
-      <c r="AA55" s="24"/>
-      <c r="AB55" s="24"/>
+      <c r="B55" s="76"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="77"/>
+      <c r="E55" s="77"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="77"/>
+      <c r="I55" s="77"/>
+      <c r="J55" s="77"/>
+      <c r="K55" s="77"/>
+      <c r="L55" s="77"/>
+      <c r="M55" s="77"/>
+      <c r="N55" s="77"/>
+      <c r="O55" s="77"/>
+      <c r="P55" s="77"/>
+      <c r="Q55" s="77"/>
+      <c r="R55" s="77"/>
+      <c r="S55" s="77"/>
+      <c r="T55" s="78"/>
+      <c r="W55" s="32"/>
+      <c r="X55" s="22"/>
+      <c r="Y55" s="22"/>
+      <c r="Z55" s="22"/>
+      <c r="AA55" s="22"/>
+      <c r="AB55" s="22"/>
     </row>
     <row r="56" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B56" s="78"/>
-      <c r="C56" s="79"/>
-      <c r="D56" s="79"/>
-      <c r="E56" s="79"/>
-      <c r="F56" s="79"/>
-      <c r="G56" s="79"/>
-      <c r="H56" s="79"/>
-      <c r="I56" s="79"/>
-      <c r="J56" s="79"/>
-      <c r="K56" s="79"/>
-      <c r="L56" s="79"/>
-      <c r="M56" s="79"/>
-      <c r="N56" s="79"/>
-      <c r="O56" s="79"/>
-      <c r="P56" s="79"/>
-      <c r="Q56" s="79"/>
-      <c r="R56" s="79"/>
-      <c r="S56" s="79"/>
-      <c r="T56" s="80"/>
+      <c r="B56" s="76"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="77"/>
+      <c r="E56" s="77"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="77"/>
+      <c r="I56" s="77"/>
+      <c r="J56" s="77"/>
+      <c r="K56" s="77"/>
+      <c r="L56" s="77"/>
+      <c r="M56" s="77"/>
+      <c r="N56" s="77"/>
+      <c r="O56" s="77"/>
+      <c r="P56" s="77"/>
+      <c r="Q56" s="77"/>
+      <c r="R56" s="77"/>
+      <c r="S56" s="77"/>
+      <c r="T56" s="78"/>
       <c r="W56" s="13"/>
-      <c r="X56" s="24"/>
-      <c r="Y56" s="24"/>
-      <c r="Z56" s="24"/>
-      <c r="AA56" s="24"/>
-      <c r="AB56" s="24"/>
+      <c r="X56" s="22"/>
+      <c r="Y56" s="22"/>
+      <c r="Z56" s="22"/>
+      <c r="AA56" s="22"/>
+      <c r="AB56" s="22"/>
     </row>
     <row r="57" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B57" s="78"/>
-      <c r="C57" s="79"/>
-      <c r="D57" s="79"/>
-      <c r="E57" s="79"/>
-      <c r="F57" s="79"/>
-      <c r="G57" s="79"/>
-      <c r="H57" s="79"/>
-      <c r="I57" s="79"/>
-      <c r="J57" s="79"/>
-      <c r="K57" s="79"/>
-      <c r="L57" s="79"/>
-      <c r="M57" s="79"/>
-      <c r="N57" s="79"/>
-      <c r="O57" s="79"/>
-      <c r="P57" s="79"/>
-      <c r="Q57" s="79"/>
-      <c r="R57" s="79"/>
-      <c r="S57" s="79"/>
-      <c r="T57" s="80"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="77"/>
+      <c r="E57" s="77"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="77"/>
+      <c r="I57" s="77"/>
+      <c r="J57" s="77"/>
+      <c r="K57" s="77"/>
+      <c r="L57" s="77"/>
+      <c r="M57" s="77"/>
+      <c r="N57" s="77"/>
+      <c r="O57" s="77"/>
+      <c r="P57" s="77"/>
+      <c r="Q57" s="77"/>
+      <c r="R57" s="77"/>
+      <c r="S57" s="77"/>
+      <c r="T57" s="78"/>
     </row>
     <row r="58" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B58" s="78"/>
-      <c r="C58" s="79"/>
-      <c r="D58" s="79"/>
-      <c r="E58" s="79"/>
-      <c r="F58" s="79"/>
-      <c r="G58" s="79"/>
-      <c r="H58" s="79"/>
-      <c r="I58" s="79"/>
-      <c r="J58" s="79"/>
-      <c r="K58" s="79"/>
-      <c r="L58" s="79"/>
-      <c r="M58" s="79"/>
-      <c r="N58" s="79"/>
-      <c r="O58" s="79"/>
-      <c r="P58" s="79"/>
-      <c r="Q58" s="79"/>
-      <c r="R58" s="79"/>
-      <c r="S58" s="79"/>
-      <c r="T58" s="80"/>
+      <c r="B58" s="76"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="77"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="77"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="77"/>
+      <c r="L58" s="77"/>
+      <c r="M58" s="77"/>
+      <c r="N58" s="77"/>
+      <c r="O58" s="77"/>
+      <c r="P58" s="77"/>
+      <c r="Q58" s="77"/>
+      <c r="R58" s="77"/>
+      <c r="S58" s="77"/>
+      <c r="T58" s="78"/>
     </row>
     <row r="59" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B59" s="78"/>
-      <c r="C59" s="79"/>
-      <c r="D59" s="79"/>
-      <c r="E59" s="79"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="79"/>
-      <c r="H59" s="79"/>
-      <c r="I59" s="79"/>
-      <c r="J59" s="79"/>
-      <c r="K59" s="79"/>
-      <c r="L59" s="79"/>
-      <c r="M59" s="79"/>
-      <c r="N59" s="79"/>
-      <c r="O59" s="79"/>
-      <c r="P59" s="79"/>
-      <c r="Q59" s="79"/>
-      <c r="R59" s="79"/>
-      <c r="S59" s="79"/>
-      <c r="T59" s="80"/>
+      <c r="B59" s="76"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="77"/>
+      <c r="E59" s="77"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="77"/>
+      <c r="I59" s="77"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="77"/>
+      <c r="L59" s="77"/>
+      <c r="M59" s="77"/>
+      <c r="N59" s="77"/>
+      <c r="O59" s="77"/>
+      <c r="P59" s="77"/>
+      <c r="Q59" s="77"/>
+      <c r="R59" s="77"/>
+      <c r="S59" s="77"/>
+      <c r="T59" s="78"/>
     </row>
     <row r="60" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B60" s="78"/>
-      <c r="C60" s="79"/>
-      <c r="D60" s="79"/>
-      <c r="E60" s="79"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="79"/>
-      <c r="H60" s="79"/>
-      <c r="I60" s="79"/>
-      <c r="J60" s="79"/>
-      <c r="K60" s="79"/>
-      <c r="L60" s="79"/>
-      <c r="M60" s="79"/>
-      <c r="N60" s="79"/>
-      <c r="O60" s="79"/>
-      <c r="P60" s="79"/>
-      <c r="Q60" s="79"/>
-      <c r="R60" s="79"/>
-      <c r="S60" s="79"/>
-      <c r="T60" s="80"/>
+      <c r="B60" s="76"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="77"/>
+      <c r="E60" s="77"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="77"/>
+      <c r="I60" s="77"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="77"/>
+      <c r="L60" s="77"/>
+      <c r="M60" s="77"/>
+      <c r="N60" s="77"/>
+      <c r="O60" s="77"/>
+      <c r="P60" s="77"/>
+      <c r="Q60" s="77"/>
+      <c r="R60" s="77"/>
+      <c r="S60" s="77"/>
+      <c r="T60" s="78"/>
     </row>
     <row r="61" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B61" s="78"/>
-      <c r="C61" s="79"/>
-      <c r="D61" s="79"/>
-      <c r="E61" s="79"/>
-      <c r="F61" s="79"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="79"/>
-      <c r="I61" s="79"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="79"/>
-      <c r="M61" s="79"/>
-      <c r="N61" s="79"/>
-      <c r="O61" s="79"/>
-      <c r="P61" s="79"/>
-      <c r="Q61" s="79"/>
-      <c r="R61" s="79"/>
-      <c r="S61" s="79"/>
-      <c r="T61" s="80"/>
+      <c r="B61" s="76"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="77"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="77"/>
+      <c r="I61" s="77"/>
+      <c r="J61" s="77"/>
+      <c r="K61" s="77"/>
+      <c r="L61" s="77"/>
+      <c r="M61" s="77"/>
+      <c r="N61" s="77"/>
+      <c r="O61" s="77"/>
+      <c r="P61" s="77"/>
+      <c r="Q61" s="77"/>
+      <c r="R61" s="77"/>
+      <c r="S61" s="77"/>
+      <c r="T61" s="78"/>
     </row>
     <row r="62" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B62" s="78"/>
-      <c r="C62" s="79"/>
-      <c r="D62" s="79"/>
-      <c r="E62" s="79"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="79"/>
-      <c r="I62" s="79"/>
-      <c r="J62" s="79"/>
-      <c r="K62" s="79"/>
-      <c r="L62" s="79"/>
-      <c r="M62" s="79"/>
-      <c r="N62" s="79"/>
-      <c r="O62" s="79"/>
-      <c r="P62" s="79"/>
-      <c r="Q62" s="79"/>
-      <c r="R62" s="79"/>
-      <c r="S62" s="79"/>
-      <c r="T62" s="80"/>
+      <c r="B62" s="76"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="77"/>
+      <c r="E62" s="77"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="77"/>
+      <c r="I62" s="77"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="77"/>
+      <c r="M62" s="77"/>
+      <c r="N62" s="77"/>
+      <c r="O62" s="77"/>
+      <c r="P62" s="77"/>
+      <c r="Q62" s="77"/>
+      <c r="R62" s="77"/>
+      <c r="S62" s="77"/>
+      <c r="T62" s="78"/>
     </row>
     <row r="63" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B63" s="78"/>
-      <c r="C63" s="79"/>
-      <c r="D63" s="79"/>
-      <c r="E63" s="79"/>
-      <c r="F63" s="79"/>
-      <c r="G63" s="79"/>
-      <c r="H63" s="79"/>
-      <c r="I63" s="79"/>
-      <c r="J63" s="79"/>
-      <c r="K63" s="79"/>
-      <c r="L63" s="79"/>
-      <c r="M63" s="79"/>
-      <c r="N63" s="79"/>
-      <c r="O63" s="79"/>
-      <c r="P63" s="79"/>
-      <c r="Q63" s="79"/>
-      <c r="R63" s="79"/>
-      <c r="S63" s="79"/>
-      <c r="T63" s="80"/>
+      <c r="B63" s="76"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="77"/>
+      <c r="E63" s="77"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="77"/>
+      <c r="I63" s="77"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="77"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="77"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="77"/>
+      <c r="P63" s="77"/>
+      <c r="Q63" s="77"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="77"/>
+      <c r="T63" s="78"/>
     </row>
     <row r="64" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B64" s="81"/>
-      <c r="C64" s="82"/>
-      <c r="D64" s="82"/>
-      <c r="E64" s="82"/>
-      <c r="F64" s="82"/>
-      <c r="G64" s="82"/>
-      <c r="H64" s="82"/>
-      <c r="I64" s="82"/>
-      <c r="J64" s="82"/>
-      <c r="K64" s="82"/>
-      <c r="L64" s="82"/>
-      <c r="M64" s="82"/>
-      <c r="N64" s="82"/>
-      <c r="O64" s="82"/>
-      <c r="P64" s="82"/>
-      <c r="Q64" s="82"/>
-      <c r="R64" s="82"/>
-      <c r="S64" s="82"/>
-      <c r="T64" s="83"/>
+      <c r="B64" s="79"/>
+      <c r="C64" s="80"/>
+      <c r="D64" s="80"/>
+      <c r="E64" s="80"/>
+      <c r="F64" s="80"/>
+      <c r="G64" s="80"/>
+      <c r="H64" s="80"/>
+      <c r="I64" s="80"/>
+      <c r="J64" s="80"/>
+      <c r="K64" s="80"/>
+      <c r="L64" s="80"/>
+      <c r="M64" s="80"/>
+      <c r="N64" s="80"/>
+      <c r="O64" s="80"/>
+      <c r="P64" s="80"/>
+      <c r="Q64" s="80"/>
+      <c r="R64" s="80"/>
+      <c r="S64" s="80"/>
+      <c r="T64" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="97">
